--- a/product-definitions/spreadsheet/boundary-layer-thickness-ceilometer.xlsx
+++ b/product-definitions/spreadsheet/boundary-layer-thickness-ceilometer.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="global-attributes-specific" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="dimensions-specific" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="variables-specific" sheetId="3" r:id="rId5"/>
+    <sheet state="visible" name="global-attributes-specific" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="dimensions-specific" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="variables-specific" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -246,7 +246,7 @@
     <t>Window Contamination (mV as measured by ADC: 0 - 2500)</t>
   </si>
   <si>
-    <t>window_transmttance</t>
+    <t>window_transmittance</t>
   </si>
   <si>
     <t>Window Transmittance, % of nominal value</t>
@@ -273,7 +273,7 @@
     <t>byte</t>
   </si>
   <si>
-    <t>Data Quality flag: Cloud Base</t>
+    <t>Data Quality flag</t>
   </si>
   <si>
     <t>flag_values</t>
@@ -298,11 +298,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -311,9 +312,11 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -327,12 +330,23 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
-      <name val="Monospace"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -355,16 +369,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <right/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -386,17 +397,14 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -405,71 +413,55 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,18 +483,212 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="29.14"/>
-    <col customWidth="1" min="3" max="3" width="29.29"/>
-    <col customWidth="1" min="4" max="4" width="27.71"/>
-    <col customWidth="1" min="5" max="5" width="29.29"/>
-    <col customWidth="1" min="6" max="6" width="28.86"/>
+    <col customWidth="1" min="1" max="2" width="25.5"/>
+    <col customWidth="1" min="3" max="3" width="25.63"/>
+    <col customWidth="1" min="4" max="4" width="24.25"/>
+    <col customWidth="1" min="5" max="5" width="25.63"/>
+    <col customWidth="1" min="6" max="6" width="25.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,6 +823,986 @@
       </c>
       <c r="F8" s="3"/>
     </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -647,12 +1813,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="18.14"/>
-    <col customWidth="1" min="3" max="3" width="45.57"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.88"/>
+    <col customWidth="1" min="3" max="3" width="39.88"/>
+    <col customWidth="1" min="4" max="23" width="7.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
@@ -685,43 +1851,37 @@
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
     </row>
     <row r="2" ht="12.0" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>1.0</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
     </row>
     <row r="3" ht="12.0" customHeight="1"/>
     <row r="4" ht="12.0" customHeight="1"/>
@@ -941,786 +2101,786 @@
     <row r="218" ht="12.0" customHeight="1"/>
     <row r="219" ht="12.0" customHeight="1"/>
     <row r="220" ht="12.0" customHeight="1"/>
-    <row r="221" ht="12.0" customHeight="1"/>
-    <row r="222" ht="12.0" customHeight="1"/>
-    <row r="223" ht="12.0" customHeight="1"/>
-    <row r="224" ht="12.0" customHeight="1"/>
-    <row r="225" ht="12.0" customHeight="1"/>
-    <row r="226" ht="12.0" customHeight="1"/>
-    <row r="227" ht="12.0" customHeight="1"/>
-    <row r="228" ht="12.0" customHeight="1"/>
-    <row r="229" ht="12.0" customHeight="1"/>
-    <row r="230" ht="12.0" customHeight="1"/>
-    <row r="231" ht="12.0" customHeight="1"/>
-    <row r="232" ht="12.0" customHeight="1"/>
-    <row r="233" ht="12.0" customHeight="1"/>
-    <row r="234" ht="12.0" customHeight="1"/>
-    <row r="235" ht="12.0" customHeight="1"/>
-    <row r="236" ht="12.0" customHeight="1"/>
-    <row r="237" ht="12.0" customHeight="1"/>
-    <row r="238" ht="12.0" customHeight="1"/>
-    <row r="239" ht="12.0" customHeight="1"/>
-    <row r="240" ht="12.0" customHeight="1"/>
-    <row r="241" ht="12.0" customHeight="1"/>
-    <row r="242" ht="12.0" customHeight="1"/>
-    <row r="243" ht="12.0" customHeight="1"/>
-    <row r="244" ht="12.0" customHeight="1"/>
-    <row r="245" ht="12.0" customHeight="1"/>
-    <row r="246" ht="12.0" customHeight="1"/>
-    <row r="247" ht="12.0" customHeight="1"/>
-    <row r="248" ht="12.0" customHeight="1"/>
-    <row r="249" ht="12.0" customHeight="1"/>
-    <row r="250" ht="12.0" customHeight="1"/>
-    <row r="251" ht="12.0" customHeight="1"/>
-    <row r="252" ht="12.0" customHeight="1"/>
-    <row r="253" ht="12.0" customHeight="1"/>
-    <row r="254" ht="12.0" customHeight="1"/>
-    <row r="255" ht="12.0" customHeight="1"/>
-    <row r="256" ht="12.0" customHeight="1"/>
-    <row r="257" ht="12.0" customHeight="1"/>
-    <row r="258" ht="12.0" customHeight="1"/>
-    <row r="259" ht="12.0" customHeight="1"/>
-    <row r="260" ht="12.0" customHeight="1"/>
-    <row r="261" ht="12.0" customHeight="1"/>
-    <row r="262" ht="12.0" customHeight="1"/>
-    <row r="263" ht="12.0" customHeight="1"/>
-    <row r="264" ht="12.0" customHeight="1"/>
-    <row r="265" ht="12.0" customHeight="1"/>
-    <row r="266" ht="12.0" customHeight="1"/>
-    <row r="267" ht="12.0" customHeight="1"/>
-    <row r="268" ht="12.0" customHeight="1"/>
-    <row r="269" ht="12.0" customHeight="1"/>
-    <row r="270" ht="12.0" customHeight="1"/>
-    <row r="271" ht="12.0" customHeight="1"/>
-    <row r="272" ht="12.0" customHeight="1"/>
-    <row r="273" ht="12.0" customHeight="1"/>
-    <row r="274" ht="12.0" customHeight="1"/>
-    <row r="275" ht="12.0" customHeight="1"/>
-    <row r="276" ht="12.0" customHeight="1"/>
-    <row r="277" ht="12.0" customHeight="1"/>
-    <row r="278" ht="12.0" customHeight="1"/>
-    <row r="279" ht="12.0" customHeight="1"/>
-    <row r="280" ht="12.0" customHeight="1"/>
-    <row r="281" ht="12.0" customHeight="1"/>
-    <row r="282" ht="12.0" customHeight="1"/>
-    <row r="283" ht="12.0" customHeight="1"/>
-    <row r="284" ht="12.0" customHeight="1"/>
-    <row r="285" ht="12.0" customHeight="1"/>
-    <row r="286" ht="12.0" customHeight="1"/>
-    <row r="287" ht="12.0" customHeight="1"/>
-    <row r="288" ht="12.0" customHeight="1"/>
-    <row r="289" ht="12.0" customHeight="1"/>
-    <row r="290" ht="12.0" customHeight="1"/>
-    <row r="291" ht="12.0" customHeight="1"/>
-    <row r="292" ht="12.0" customHeight="1"/>
-    <row r="293" ht="12.0" customHeight="1"/>
-    <row r="294" ht="12.0" customHeight="1"/>
-    <row r="295" ht="12.0" customHeight="1"/>
-    <row r="296" ht="12.0" customHeight="1"/>
-    <row r="297" ht="12.0" customHeight="1"/>
-    <row r="298" ht="12.0" customHeight="1"/>
-    <row r="299" ht="12.0" customHeight="1"/>
-    <row r="300" ht="12.0" customHeight="1"/>
-    <row r="301" ht="12.0" customHeight="1"/>
-    <row r="302" ht="12.0" customHeight="1"/>
-    <row r="303" ht="12.0" customHeight="1"/>
-    <row r="304" ht="12.0" customHeight="1"/>
-    <row r="305" ht="12.0" customHeight="1"/>
-    <row r="306" ht="12.0" customHeight="1"/>
-    <row r="307" ht="12.0" customHeight="1"/>
-    <row r="308" ht="12.0" customHeight="1"/>
-    <row r="309" ht="12.0" customHeight="1"/>
-    <row r="310" ht="12.0" customHeight="1"/>
-    <row r="311" ht="12.0" customHeight="1"/>
-    <row r="312" ht="12.0" customHeight="1"/>
-    <row r="313" ht="12.0" customHeight="1"/>
-    <row r="314" ht="12.0" customHeight="1"/>
-    <row r="315" ht="12.0" customHeight="1"/>
-    <row r="316" ht="12.0" customHeight="1"/>
-    <row r="317" ht="12.0" customHeight="1"/>
-    <row r="318" ht="12.0" customHeight="1"/>
-    <row r="319" ht="12.0" customHeight="1"/>
-    <row r="320" ht="12.0" customHeight="1"/>
-    <row r="321" ht="12.0" customHeight="1"/>
-    <row r="322" ht="12.0" customHeight="1"/>
-    <row r="323" ht="12.0" customHeight="1"/>
-    <row r="324" ht="12.0" customHeight="1"/>
-    <row r="325" ht="12.0" customHeight="1"/>
-    <row r="326" ht="12.0" customHeight="1"/>
-    <row r="327" ht="12.0" customHeight="1"/>
-    <row r="328" ht="12.0" customHeight="1"/>
-    <row r="329" ht="12.0" customHeight="1"/>
-    <row r="330" ht="12.0" customHeight="1"/>
-    <row r="331" ht="12.0" customHeight="1"/>
-    <row r="332" ht="12.0" customHeight="1"/>
-    <row r="333" ht="12.0" customHeight="1"/>
-    <row r="334" ht="12.0" customHeight="1"/>
-    <row r="335" ht="12.0" customHeight="1"/>
-    <row r="336" ht="12.0" customHeight="1"/>
-    <row r="337" ht="12.0" customHeight="1"/>
-    <row r="338" ht="12.0" customHeight="1"/>
-    <row r="339" ht="12.0" customHeight="1"/>
-    <row r="340" ht="12.0" customHeight="1"/>
-    <row r="341" ht="12.0" customHeight="1"/>
-    <row r="342" ht="12.0" customHeight="1"/>
-    <row r="343" ht="12.0" customHeight="1"/>
-    <row r="344" ht="12.0" customHeight="1"/>
-    <row r="345" ht="12.0" customHeight="1"/>
-    <row r="346" ht="12.0" customHeight="1"/>
-    <row r="347" ht="12.0" customHeight="1"/>
-    <row r="348" ht="12.0" customHeight="1"/>
-    <row r="349" ht="12.0" customHeight="1"/>
-    <row r="350" ht="12.0" customHeight="1"/>
-    <row r="351" ht="12.0" customHeight="1"/>
-    <row r="352" ht="12.0" customHeight="1"/>
-    <row r="353" ht="12.0" customHeight="1"/>
-    <row r="354" ht="12.0" customHeight="1"/>
-    <row r="355" ht="12.0" customHeight="1"/>
-    <row r="356" ht="12.0" customHeight="1"/>
-    <row r="357" ht="12.0" customHeight="1"/>
-    <row r="358" ht="12.0" customHeight="1"/>
-    <row r="359" ht="12.0" customHeight="1"/>
-    <row r="360" ht="12.0" customHeight="1"/>
-    <row r="361" ht="12.0" customHeight="1"/>
-    <row r="362" ht="12.0" customHeight="1"/>
-    <row r="363" ht="12.0" customHeight="1"/>
-    <row r="364" ht="12.0" customHeight="1"/>
-    <row r="365" ht="12.0" customHeight="1"/>
-    <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
-    <row r="994" ht="12.0" customHeight="1"/>
-    <row r="995" ht="12.0" customHeight="1"/>
-    <row r="996" ht="12.0" customHeight="1"/>
-    <row r="997" ht="12.0" customHeight="1"/>
-    <row r="998" ht="12.0" customHeight="1"/>
-    <row r="999" ht="12.0" customHeight="1"/>
-    <row r="1000" ht="12.0" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1731,89 +2891,88 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="17.86"/>
-    <col customWidth="1" min="3" max="3" width="26.71"/>
-    <col customWidth="1" min="4" max="4" width="18.0"/>
-    <col customWidth="1" min="5" max="5" width="18.29"/>
-    <col customWidth="1" min="6" max="6" width="17.71"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.63"/>
+    <col customWidth="1" min="3" max="3" width="23.38"/>
+    <col customWidth="1" min="4" max="4" width="15.75"/>
+    <col customWidth="1" min="5" max="5" width="16.0"/>
+    <col customWidth="1" min="6" max="6" width="15.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" ht="12.0" customHeight="1">
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="B3" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" ht="12.0" customHeight="1">
-      <c r="B4" t="s">
+    <row r="4">
+      <c r="B4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" ht="12.0" customHeight="1">
-      <c r="B5" t="s">
+    <row r="5">
+      <c r="B5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="12.0" customHeight="1">
-      <c r="B6" t="s">
+    <row r="6">
+      <c r="B6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" ht="12.0" customHeight="1">
-      <c r="B7" t="s">
+    <row r="7">
+      <c r="B7" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" ht="12.0" customHeight="1">
-      <c r="B8" t="s">
+    <row r="8">
+      <c r="B8" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="17">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="9" ht="12.0" customHeight="1">
+    <row r="9">
       <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
@@ -1824,7 +2983,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="19"/>
     </row>
-    <row r="10" ht="12.0" customHeight="1">
+    <row r="10">
       <c r="B10" s="3" t="s">
         <v>49</v>
       </c>
@@ -1835,26 +2994,26 @@
       <c r="E10" s="3"/>
       <c r="F10" s="19"/>
     </row>
-    <row r="11" ht="12.0" customHeight="1">
-      <c r="B11" t="s">
+    <row r="11">
+      <c r="B11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" ht="12.0" customHeight="1">
-      <c r="B12" t="s">
+    <row r="12">
+      <c r="B12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" ht="12.0" customHeight="1">
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" ht="12.0" customHeight="1">
+    <row r="13">
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -1863,7 +3022,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="12.0" customHeight="1">
+    <row r="15">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -1874,7 +3033,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="12.0" customHeight="1">
+    <row r="16">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>40</v>
@@ -1885,7 +3044,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="12.0" customHeight="1">
+    <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>29</v>
@@ -1896,7 +3055,7 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="12.0" customHeight="1">
+    <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>43</v>
@@ -1907,7 +3066,7 @@
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="12.0" customHeight="1">
+    <row r="19">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>44</v>
@@ -1918,7 +3077,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="12.0" customHeight="1">
+    <row r="20">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -1929,7 +3088,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="12.0" customHeight="1">
+    <row r="21">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>47</v>
@@ -1940,7 +3099,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" ht="12.0" customHeight="1">
+    <row r="22">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>49</v>
@@ -1951,7 +3110,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" ht="12.0" customHeight="1">
+    <row r="23">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>51</v>
@@ -1962,7 +3121,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" ht="12.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>53</v>
@@ -1973,14 +3132,14 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" ht="12.0" customHeight="1">
+    <row r="25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" ht="12.0" customHeight="1">
+    <row r="26">
       <c r="A26" s="3" t="s">
         <v>60</v>
       </c>
@@ -1989,7 +3148,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" ht="12.0" customHeight="1">
+    <row r="27">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>38</v>
@@ -2000,7 +3159,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="12.0" customHeight="1">
+    <row r="28">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>40</v>
@@ -2011,7 +3170,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="12.0" customHeight="1">
+    <row r="29">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -2022,7 +3181,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="12.0" customHeight="1">
+    <row r="30">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>43</v>
@@ -2033,7 +3192,7 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="12.0" customHeight="1">
+    <row r="31">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>44</v>
@@ -2044,7 +3203,7 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="12.0" customHeight="1">
+    <row r="32">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>46</v>
@@ -2055,7 +3214,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="12.0" customHeight="1">
+    <row r="33">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>47</v>
@@ -2066,7 +3225,7 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" ht="12.0" customHeight="1">
+    <row r="34">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>49</v>
@@ -2077,7 +3236,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" ht="12.0" customHeight="1">
+    <row r="35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>51</v>
@@ -2088,7 +3247,7 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" ht="12.0" customHeight="1">
+    <row r="36">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>53</v>
@@ -2099,15 +3258,15 @@
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" ht="12.0" customHeight="1">
+    <row r="37">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" ht="12.0" customHeight="1">
-      <c r="A38" s="26" t="s">
+    <row r="38">
+      <c r="A38" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B38" s="3"/>
@@ -2115,7 +3274,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" ht="12.0" customHeight="1">
+    <row r="39">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>38</v>
@@ -2126,7 +3285,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" ht="12.0" customHeight="1">
+    <row r="40">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>40</v>
@@ -2137,7 +3296,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" ht="12.0" customHeight="1">
+    <row r="41">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -2148,29 +3307,29 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" ht="12.0" customHeight="1">
+    <row r="42">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" ht="12.0" customHeight="1">
+    <row r="43">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="26" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" ht="12.0" customHeight="1">
+    <row r="44">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>46</v>
@@ -2181,7 +3340,7 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" ht="12.0" customHeight="1">
+    <row r="45">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>47</v>
@@ -2192,7 +3351,7 @@
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" ht="12.0" customHeight="1">
+    <row r="46">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>49</v>
@@ -2203,7 +3362,7 @@
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" ht="12.0" customHeight="1">
+    <row r="47">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>51</v>
@@ -2214,7 +3373,7 @@
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" ht="12.0" customHeight="1">
+    <row r="48">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>53</v>
@@ -2225,14 +3384,14 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" ht="12.0" customHeight="1">
+    <row r="49">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" ht="12.0" customHeight="1">
+    <row r="50">
       <c r="A50" s="19" t="s">
         <v>66</v>
       </c>
@@ -2241,7 +3400,7 @@
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" ht="12.0" customHeight="1">
+    <row r="51">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>38</v>
@@ -2252,7 +3411,7 @@
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="12.0" customHeight="1">
+    <row r="52">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>40</v>
@@ -2263,18 +3422,18 @@
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="12.0" customHeight="1">
+    <row r="53">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="20" t="s">
         <v>64</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="12.0" customHeight="1">
+    <row r="54">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2285,18 +3444,18 @@
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="12.0" customHeight="1">
+    <row r="55">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="C55" s="26" t="s">
         <v>67</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="12.0" customHeight="1">
+    <row r="56">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>46</v>
@@ -2307,7 +3466,7 @@
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="12.0" customHeight="1">
+    <row r="57">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>47</v>
@@ -2318,7 +3477,7 @@
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="12.0" customHeight="1">
+    <row r="58">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>49</v>
@@ -2329,7 +3488,7 @@
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="12.0" customHeight="1">
+    <row r="59">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>51</v>
@@ -2340,7 +3499,7 @@
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="12.0" customHeight="1">
+    <row r="60">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>53</v>
@@ -2351,14 +3510,14 @@
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="12.0" customHeight="1">
+    <row r="61">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="12.0" customHeight="1">
+    <row r="62">
       <c r="A62" s="3" t="s">
         <v>68</v>
       </c>
@@ -2367,7 +3526,7 @@
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="12.0" customHeight="1">
+    <row r="63">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>38</v>
@@ -2378,7 +3537,7 @@
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="12.0" customHeight="1">
+    <row r="64">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>40</v>
@@ -2389,18 +3548,18 @@
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="12.0" customHeight="1">
+    <row r="65">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="27">
         <v>1.0</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="12.0" customHeight="1">
+    <row r="66">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>43</v>
@@ -2409,18 +3568,18 @@
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="12.0" customHeight="1">
+    <row r="67">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C67" s="28" t="s">
         <v>69</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="12.0" customHeight="1">
+    <row r="68">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>46</v>
@@ -2431,7 +3590,7 @@
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" ht="12.0" customHeight="1">
+    <row r="69">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>47</v>
@@ -2442,7 +3601,7 @@
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" ht="12.0" customHeight="1">
+    <row r="70">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>49</v>
@@ -2453,18 +3612,18 @@
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" ht="12.0" customHeight="1">
+    <row r="71">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="21" t="s">
         <v>70</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" ht="12.0" customHeight="1">
+    <row r="72">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>53</v>
@@ -2475,15 +3634,15 @@
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" ht="12.0" customHeight="1">
+    <row r="73">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" ht="12.0" customHeight="1">
-      <c r="A74" s="26" t="s">
+    <row r="74">
+      <c r="A74" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B74" s="3"/>
@@ -2491,7 +3650,7 @@
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" ht="12.0" customHeight="1">
+    <row r="75">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>38</v>
@@ -2502,29 +3661,29 @@
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" ht="12.0" customHeight="1">
+    <row r="76">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" ht="12.0" customHeight="1">
+    <row r="77">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="31" t="s">
+      <c r="C77" s="21" t="s">
         <v>57</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" ht="12.0" customHeight="1">
+    <row r="78">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>43</v>
@@ -2533,18 +3692,18 @@
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" ht="12.0" customHeight="1">
+    <row r="79">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" ht="12.0" customHeight="1">
+    <row r="80">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>46</v>
@@ -2555,7 +3714,7 @@
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" ht="12.0" customHeight="1">
+    <row r="81">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>47</v>
@@ -2566,7 +3725,7 @@
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" ht="12.0" customHeight="1">
+    <row r="82">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>49</v>
@@ -2577,36 +3736,36 @@
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" ht="12.0" customHeight="1">
-      <c r="A83" s="26"/>
+    <row r="83">
+      <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C83" s="21" t="s">
         <v>73</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" ht="12.0" customHeight="1">
+    <row r="84">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="28" t="s">
+      <c r="C84" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" ht="12.0" customHeight="1">
+    <row r="85">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
-      <c r="C85" s="26"/>
+      <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" ht="12.0" customHeight="1">
+    <row r="86">
       <c r="A86" s="19" t="s">
         <v>74</v>
       </c>
@@ -2615,29 +3774,29 @@
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" ht="12.0" customHeight="1">
+    <row r="87">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C87" s="31" t="s">
+      <c r="C87" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" ht="12.0" customHeight="1">
+    <row r="88">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C88" s="28" t="s">
+      <c r="C88" s="20" t="s">
         <v>56</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" ht="12.0" customHeight="1">
+    <row r="89">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>29</v>
@@ -2648,29 +3807,29 @@
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" ht="12.0" customHeight="1">
+    <row r="90">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C90" s="28"/>
+      <c r="C90" s="20"/>
       <c r="D90" s="19" t="s">
         <v>74</v>
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" ht="12.0" customHeight="1">
+    <row r="91">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="32" t="s">
+      <c r="C91" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D91" s="33"/>
+      <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" ht="12.0" customHeight="1">
+    <row r="92">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>46</v>
@@ -2681,7 +3840,7 @@
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" ht="12.0" customHeight="1">
+    <row r="93">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>47</v>
@@ -2692,7 +3851,7 @@
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" ht="12.0" customHeight="1">
+    <row r="94">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>49</v>
@@ -2703,7 +3862,7 @@
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" ht="12.0" customHeight="1">
+    <row r="95">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>51</v>
@@ -2714,7 +3873,7 @@
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" ht="12.0" customHeight="1">
+    <row r="96">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>53</v>
@@ -2725,15 +3884,15 @@
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" ht="12.0" customHeight="1">
+    <row r="97">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="19" t="s">
+    <row r="98">
+      <c r="A98" s="29" t="s">
         <v>77</v>
       </c>
       <c r="B98" s="3"/>
@@ -2741,18 +3900,18 @@
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" ht="12.0" customHeight="1">
+    <row r="99">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C99" s="31" t="s">
+      <c r="C99" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" ht="12.0" customHeight="1">
+    <row r="100">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>40</v>
@@ -2763,18 +3922,18 @@
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" ht="12.0" customHeight="1">
+    <row r="101">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C101" s="21" t="s">
         <v>57</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" ht="12.0" customHeight="1">
+    <row r="102">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>43</v>
@@ -2783,18 +3942,18 @@
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" ht="12.0" customHeight="1">
+    <row r="103">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="32" t="s">
+      <c r="C103" s="26" t="s">
         <v>78</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" ht="12.0" customHeight="1">
+    <row r="104">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>46</v>
@@ -2805,7 +3964,7 @@
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" ht="12.0" customHeight="1">
+    <row r="105">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>47</v>
@@ -2816,7 +3975,7 @@
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" ht="12.0" customHeight="1">
+    <row r="106">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>49</v>
@@ -2827,7 +3986,7 @@
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" ht="12.0" customHeight="1">
+    <row r="107">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>51</v>
@@ -2838,7 +3997,7 @@
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" ht="12.0" customHeight="1">
+    <row r="108">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>53</v>
@@ -2849,14 +4008,14 @@
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" ht="12.0" customHeight="1">
+    <row r="109">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" ht="12.0" customHeight="1">
+    <row r="110">
       <c r="A110" s="3" t="s">
         <v>79</v>
       </c>
@@ -2865,18 +4024,18 @@
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" ht="12.0" customHeight="1">
+    <row r="111">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C111" s="31" t="s">
+      <c r="C111" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" ht="12.0" customHeight="1">
+    <row r="112">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>40</v>
@@ -2887,18 +4046,18 @@
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" ht="12.0" customHeight="1">
+    <row r="113">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="31" t="s">
+      <c r="C113" s="21" t="s">
         <v>75</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" ht="12.0" customHeight="1">
+    <row r="114">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>43</v>
@@ -2909,7 +4068,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" ht="12.0" customHeight="1">
+    <row r="115">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>44</v>
@@ -2917,10 +4076,10 @@
       <c r="C115" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D115" s="33"/>
+      <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" ht="12.0" customHeight="1">
+    <row r="116">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>46</v>
@@ -2931,7 +4090,7 @@
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" ht="12.0" customHeight="1">
+    <row r="117">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>47</v>
@@ -2942,7 +4101,7 @@
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" ht="12.0" customHeight="1">
+    <row r="118">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>49</v>
@@ -2953,7 +4112,7 @@
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" ht="12.0" customHeight="1">
+    <row r="119">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>51</v>
@@ -2964,7 +4123,7 @@
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" ht="12.0" customHeight="1">
+    <row r="120">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>53</v>
@@ -2975,14 +4134,14 @@
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" ht="12.0" customHeight="1">
+    <row r="121">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" ht="12.0" customHeight="1">
+    <row r="122">
       <c r="A122" s="3" t="s">
         <v>81</v>
       </c>
@@ -2991,18 +4150,18 @@
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" ht="12.0" customHeight="1">
+    <row r="123">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="31" t="s">
+      <c r="C123" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" ht="12.0" customHeight="1">
+    <row r="124">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>40</v>
@@ -3013,18 +4172,18 @@
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" ht="12.0" customHeight="1">
+    <row r="125">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="C125" s="21" t="s">
         <v>82</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" ht="12.0" customHeight="1">
+    <row r="126">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>43</v>
@@ -3033,7 +4192,7 @@
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" ht="12.0" customHeight="1">
+    <row r="127">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>44</v>
@@ -3044,7 +4203,7 @@
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" ht="12.0" customHeight="1">
+    <row r="128">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>46</v>
@@ -3055,7 +4214,7 @@
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" ht="12.0" customHeight="1">
+    <row r="129">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>47</v>
@@ -3066,7 +4225,7 @@
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" ht="12.0" customHeight="1">
+    <row r="130">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>49</v>
@@ -3077,7 +4236,7 @@
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" ht="12.0" customHeight="1">
+    <row r="131">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>51</v>
@@ -3088,7 +4247,7 @@
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" ht="12.0" customHeight="1">
+    <row r="132">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>53</v>
@@ -3099,14 +4258,14 @@
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" ht="12.0" customHeight="1">
+    <row r="133">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" ht="12.0" customHeight="1">
+    <row r="134">
       <c r="A134" s="3" t="s">
         <v>84</v>
       </c>
@@ -3115,71 +4274,71 @@
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" ht="12.0" customHeight="1">
+    <row r="135">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="31" t="s">
+      <c r="C135" s="21" t="s">
         <v>85</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" ht="12.0" customHeight="1">
+    <row r="136">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C136" s="34" t="s">
-        <v>41</v>
+      <c r="C136" s="30" t="s">
+        <v>56</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" ht="12.0" customHeight="1">
+    <row r="137">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="35">
+      <c r="C137" s="27">
         <v>1.0</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" ht="12.0" customHeight="1">
+    <row r="138">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C138" s="31"/>
+      <c r="C138" s="21"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" ht="12.0" customHeight="1">
+    <row r="139">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C139" s="31" t="s">
+      <c r="C139" s="21" t="s">
         <v>86</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" ht="12.0" customHeight="1">
+    <row r="140">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C140" s="31" t="s">
+      <c r="C140" s="21" t="s">
         <v>88</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" ht="12.0" customHeight="1">
+    <row r="141">
       <c r="A141" s="3"/>
       <c r="B141" s="20" t="s">
         <v>89</v>
@@ -3187,8 +4346,8 @@
       <c r="C141" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D141" s="33"/>
-      <c r="E141" s="33"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
     </row>
     <row r="142" ht="12.0" customHeight="1">
       <c r="A142" s="3"/>
@@ -3486,658 +4645,665 @@
     <row r="339" ht="12.0" customHeight="1"/>
     <row r="340" ht="12.0" customHeight="1"/>
     <row r="341" ht="12.0" customHeight="1"/>
-    <row r="342" ht="12.0" customHeight="1"/>
-    <row r="343" ht="12.0" customHeight="1"/>
-    <row r="344" ht="12.0" customHeight="1"/>
-    <row r="345" ht="12.0" customHeight="1"/>
-    <row r="346" ht="12.0" customHeight="1"/>
-    <row r="347" ht="12.0" customHeight="1"/>
-    <row r="348" ht="12.0" customHeight="1"/>
-    <row r="349" ht="12.0" customHeight="1"/>
-    <row r="350" ht="12.0" customHeight="1"/>
-    <row r="351" ht="12.0" customHeight="1"/>
-    <row r="352" ht="12.0" customHeight="1"/>
-    <row r="353" ht="12.0" customHeight="1"/>
-    <row r="354" ht="12.0" customHeight="1"/>
-    <row r="355" ht="12.0" customHeight="1"/>
-    <row r="356" ht="12.0" customHeight="1"/>
-    <row r="357" ht="12.0" customHeight="1"/>
-    <row r="358" ht="12.0" customHeight="1"/>
-    <row r="359" ht="12.0" customHeight="1"/>
-    <row r="360" ht="12.0" customHeight="1"/>
-    <row r="361" ht="12.0" customHeight="1"/>
-    <row r="362" ht="12.0" customHeight="1"/>
-    <row r="363" ht="12.0" customHeight="1"/>
-    <row r="364" ht="12.0" customHeight="1"/>
-    <row r="365" ht="12.0" customHeight="1"/>
-    <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/product-definitions/spreadsheet/boundary-layer-thickness-ceilometer.xlsx
+++ b/product-definitions/spreadsheet/boundary-layer-thickness-ceilometer.xlsx
@@ -298,7 +298,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -343,11 +343,6 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -375,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -414,12 +409,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -456,12 +448,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2936,7 +2922,7 @@
       <c r="B4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2968,7 +2954,7 @@
       <c r="B8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2976,23 +2962,23 @@
       <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="19"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="19"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11">
       <c r="B11" s="14" t="s">
@@ -3018,7 +3004,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="20"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
@@ -3027,7 +3013,7 @@
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="3"/>
@@ -3038,7 +3024,7 @@
       <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="3"/>
@@ -3049,7 +3035,7 @@
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="3"/>
@@ -3060,7 +3046,7 @@
       <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="20"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="3" t="s">
         <v>55</v>
       </c>
@@ -3071,7 +3057,7 @@
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>58</v>
       </c>
       <c r="D19" s="3"/>
@@ -3082,232 +3068,232 @@
       <c r="B20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="20"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="19" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="20"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="19" t="s">
         <v>64</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -3318,122 +3304,122 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="25" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50">
-      <c r="A50" s="19" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="18" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="3"/>
-      <c r="C50" s="20"/>
+      <c r="C50" s="19"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="19" t="s">
         <v>64</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -3444,122 +3430,122 @@
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="25" t="s">
         <v>67</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B62" s="3"/>
-      <c r="C62" s="20"/>
+      <c r="C62" s="19"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C63" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="26">
         <v>1.0</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>43</v>
@@ -3568,122 +3554,122 @@
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="27" t="s">
         <v>69</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="23">
+      <c r="C68" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" s="20" t="s">
         <v>70</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B74" s="3"/>
-      <c r="C74" s="20"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C75" s="21" t="s">
+      <c r="C75" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="20" t="s">
         <v>57</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>43</v>
@@ -3692,658 +3678,658 @@
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="25" t="s">
         <v>72</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C80" s="23">
+      <c r="C80" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C82" s="25" t="s">
+      <c r="C82" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C83" s="20" t="s">
         <v>73</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86">
-      <c r="A86" s="19" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="18" t="s">
         <v>74</v>
       </c>
       <c r="B86" s="3"/>
-      <c r="C86" s="20"/>
+      <c r="C86" s="19"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C87" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="21" t="s">
+      <c r="C89" s="20" t="s">
         <v>75</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C90" s="20"/>
-      <c r="D90" s="19" t="s">
+      <c r="C90" s="19"/>
+      <c r="D90" s="18" t="s">
         <v>74</v>
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="26" t="s">
+      <c r="C91" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C92" s="23">
+      <c r="C92" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C93" s="25" t="s">
+      <c r="C93" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C94" s="25" t="s">
+      <c r="C94" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="20" t="s">
+      <c r="C95" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C96" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98">
-      <c r="A98" s="29" t="s">
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="18" t="s">
         <v>77</v>
       </c>
       <c r="B98" s="3"/>
-      <c r="C98" s="20"/>
+      <c r="C98" s="19"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C99" s="21" t="s">
+      <c r="C99" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C100" s="20" t="s">
+      <c r="C100" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" s="20" t="s">
         <v>57</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C102" s="20"/>
+      <c r="C102" s="19"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="26" t="s">
+      <c r="C103" s="25" t="s">
         <v>78</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C104" s="23">
+      <c r="C104" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C105" s="25" t="s">
+      <c r="C105" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C106" s="25" t="s">
+      <c r="C106" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C107" s="20" t="s">
+      <c r="C107" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B110" s="3"/>
-      <c r="C110" s="20"/>
+      <c r="C110" s="19"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="20" t="s">
         <v>75</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C114" s="20"/>
+      <c r="C114" s="19"/>
       <c r="D114" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="18" t="s">
         <v>80</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C116" s="23">
+      <c r="C116" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C117" s="25" t="s">
+      <c r="C117" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C118" s="25" t="s">
+      <c r="C118" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C119" s="20" t="s">
+      <c r="C119" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="C120" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B122" s="3"/>
-      <c r="C122" s="20"/>
+      <c r="C122" s="19"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C124" s="20" t="s">
+      <c r="C124" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C125" s="20" t="s">
         <v>82</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C126" s="20"/>
+      <c r="C126" s="19"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C127" s="19" t="s">
+      <c r="C127" s="18" t="s">
         <v>83</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C128" s="23">
+      <c r="C128" s="22">
         <v>-1.0E20</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C129" s="25" t="s">
+      <c r="C129" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="25" t="s">
+      <c r="C130" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C131" s="20" t="s">
+      <c r="C131" s="19" t="s">
         <v>52</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C132" s="20" t="s">
+      <c r="C132" s="19" t="s">
         <v>54</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B134" s="3"/>
-      <c r="C134" s="20"/>
+      <c r="C134" s="19"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C135" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C136" s="30" t="s">
+      <c r="C136" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="27">
+      <c r="C137" s="26">
         <v>1.0</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C138" s="21"/>
+      <c r="C138" s="20"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" s="20" t="s">
         <v>86</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="20" t="s">
         <v>88</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
-      <c r="B141" s="20" t="s">
+      <c r="B141" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C141" s="22" t="s">
+      <c r="C141" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D141" s="3"/>
